--- a/common/djangoapps/student/management/commands/static/bulk_upload.xlsx
+++ b/common/djangoapps/student/management/commands/static/bulk_upload.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="167">
   <si>
     <t xml:space="preserve">Grade</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">SUBJECT</t>
   </si>
   <si>
-    <t xml:space="preserve">SME</t>
+    <t xml:space="preserve">LANGUAGE</t>
   </si>
   <si>
     <t xml:space="preserve">  Lesson Name</t>
@@ -49,34 +49,478 @@
     <t xml:space="preserve">Grade 6</t>
   </si>
   <si>
-    <t xml:space="preserve">April</t>
+    <t xml:space="preserve">Social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marathi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The earth in the Solar System Part-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/ja1LHoeP7OE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Forest Using Protecting P-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Zq7VwOihOgI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Forest Using Protecting P-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/jkxEbwdF-wE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Forest Using Protecting P-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/UdTaF5ER170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Forest Using Protecting P-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Izbw_iE3Gpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture Part-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/EuyEUtV4yxk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture Part-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/ZwkeFj1hmdI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minerals, Mining, &amp; Power Resources Part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/fvfoIlE2Tsg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minerals, Mining, &amp; Power Resources Part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/V6ym7GBFaN4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minerals, Mining, &amp; Power Resources Part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/yjxBURNZhVY</t>
   </si>
   <si>
     <t xml:space="preserve">Science</t>
   </si>
   <si>
-    <t xml:space="preserve">Dhivya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motion and Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part - 1 Story of Transport and Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://youtu.be/iT0350HLakI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grade 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Part - 2 Standard units of Measurement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://youtu.be/KYUKtaW9QJI</t>
+    <t xml:space="preserve">Skeletal Movement </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/NzVSiW8ZUvc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spherical mirrors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/VsnFvigX4Z4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biodiversity &amp;Conservation Part-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/7tt49mpgzP8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood circulatory system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/PSI6AOh8FFE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blood circulatory system (continue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/iIcu2zGPidI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cell Basic unit of life</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/e82D2Zn9p7Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop production and management p-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/nx02iPp7WFA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop production and management p-1 continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/3ybSyY_fJtE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop production and management p-2 continue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/lkq6cA3v1W4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crop production and management p-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/MYma3EElKbQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Different Ecosytems part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/eVt41zov8qA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Different Ecosytems part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/6fywwuZQUZ4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Different Ecosystems Part-1(Continue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/z7nnXvXxBfU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Different Ecosystems Part-2(Continue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/9F3H9YPtpw0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biodiversity and Conservation Part-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/VKUzO9sLod8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Biodiversity &amp;Conservation Part-2(continue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/xTLbaQwOvKE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/mYwdvGSbAlY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maths</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algebraic Expression Part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/tE1jNP5JzxA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algebraic Expression Part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/4pKdclZ9cFg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algebraic Expression Part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/gwAgrZxVgH8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algebraic Expression Part 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/-Yd4BjPI_HI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics  part 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/KywwBPA7QZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics  part 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/NogolcBUxgM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics  part 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Blm_BvadN1o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics  part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/F2FGzPZUQSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics  part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/CiVmxjRQc9o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statistics  part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/rA3j9DmoZMk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grade 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Liberation movement in colonies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/fuIerO24xlw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Rivers and Water Resources P-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/0I7dBaLGox4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India- Relief Features</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/F3ESIoGemOo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Rivers Water Resources Part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Wfmc8mTONCw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemistry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactions of acids bases forming Salts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/nvxuugR6ANE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metallurgy part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/jGWR0mrlaDw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sexual Reproduction in Plants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/AXFE342YFEg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plants hormones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/NvJqHbwpnGk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinal cord &amp; Peripheral Nervous System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/bMJCN8Vy5fM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Respiration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/5coI94VOd-A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mendel's Experiments and laws</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Pkzyy6Kxti4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodic Table part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/w0uks3I8Jp0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applications of chemical Reactions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/QG3DIe8g9l8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/pot8FC7tOTA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metallurgy Part-2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/e-2abLytShQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acids, Basis, salts - Uses of Salts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acids, Basis, salts  - Uses of Salts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/oSijzZayBsQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Properties and occurrences of non metals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/k8ZC-JRURfc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">properties of metals and non metals part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">properties of metals and non metals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/1yhCRTojgsk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodic Table Part-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/xZyWhUXKIRs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodic Table Part-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/tJr6SW91q9E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chemical reaction part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/k2ZJuCxn0HE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chemical reaction part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Xd5VTPX7Blg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon &amp; compound part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/B7Be96LV7Ww</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon &amp; compound part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/nHRBi6EQ98g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemical Bonding part- 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Xj56dcB1M6Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemical Bonding part- 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/MMzZKLICad4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemical Bonding part- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/4I-mrxVW8dk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Periodic Table part 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Ne5GaArtZg8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon &amp; compound part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/ChlBuWcUlRs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian Population part 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/zLRNT_3zaOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World between world war 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/2i2iPPkWv7c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wrold between world war 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/0XxN47rpisc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Liberation Part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/wY_xEi43h4I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mass Media and history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/ca8EF8fNcbI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The population part-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/1IveOpxzv4s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">World between world war part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">world between world war part 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/ZR5WFmdvo3o</t>
   </si>
 </sst>
 </file>
@@ -86,7 +530,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -117,10 +561,30 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0D0D0D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <u val="single"/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF0563C1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -179,13 +643,21 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -196,12 +668,28 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -266,7 +754,7 @@
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF0D0D0D"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
@@ -282,110 +770,1511 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:H1048576"/>
+  <sheetFormatPr defaultColWidth="11.578125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="67.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="39.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="36.57"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="3" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="F3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="F4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="4" t="s">
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="8" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="4"/>
-    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H34" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H57" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="H58" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="H59" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="H60" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="H61" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="H62" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="H63" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="H64" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="H65" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="H66" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="H67" s="8" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="H68" s="8" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="H70" s="8" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="H72" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H74" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="https://youtu.be/iT0350HLakI"/>
-    <hyperlink ref="H3" r:id="rId2" display="https://youtu.be/KYUKtaW9QJI"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
